--- a/vietnam/vietnam_jobs_20260516.xlsx
+++ b/vietnam/vietnam_jobs_20260516.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$J$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1075,27 +1075,41 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Fulbright University Vietnam</t>
+          <t>University of Science and Technology of Hanoi - USTH</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Lecturer – English / Critical Thinking / Academic Skills</t>
+          <t>Giảng viên đại học</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hanoi, Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>60,000,000 – 85,000,000 VND/month (negotiated)</t>
+          <t>2009 tr</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Master's in English, Education or related field; university-level teaching experience; interdisciplinary liberal arts interest</t>
+          <t>Skip to main content
+LinkedIn
+Jobs
+Clear text
+Clear text
+Sign in
+Join now
+Giảng viên đại học
+University of Science and Technology of Hanoi - USTH  Hanoi, Hanoi, Vietnam
+1 day ago   Be among the first 25 applicants
+See who University of Science and Technology of Hanoi - USTH has hired for this role
+Apply
+Save
+A.   Thông tin chung 
+ Được thành lập năm 2009 trong khuôn khổ Thỏa thuận hợp tác g</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
@@ -1103,17 +1117,17 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>MA Education (ongoing), liberal arts focus, academic environment</t>
+          <t>University, Salary 2009MM VND (target), Subject match, Full-time</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Web Research</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>https://fulbright.edu.vn/careers</t>
+          <t>https://www.linkedin.com/jobs/view/4414451792</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1125,25 +1139,75 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Fulbright University Vietnam</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Lecturer – English / Critical Thinking / Academic Skills</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60,000,000 – 85,000,000 VND/month (negotiated)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Master's in English, Education or related field; university-level teaching experience; interdisciplinary liberal arts interest</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>MA Education (ongoing), liberal arts focus, academic environment</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Web Research</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://fulbright.edu.vn/careers</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Legal &amp;amp; Teaching Jobs for Foreign Teachers in Vietnam</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>[Hanoi] IELTS English Teachers| Up to 730,000 VND/hour &amp; IELTS Supplement</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Teaching at public schools across Hanoi</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>730,000 VND</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Skip to main content
 LinkedIn
@@ -1161,52 +1225,52 @@
 Use AI to assess how yo</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F15" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>High School, Salary 730000M VND, Subject match</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4405352013</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Atlantic Teacher Careers</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>[HANOI] Full-time High school/IELTS Teachers needed for our in-school teaching team</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Atlantic Teacher Careers  Hanoi, Hanoi, Vietnam</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">580,000VND </t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Skip to main content
 LinkedIn
@@ -1225,52 +1289,52 @@
 [HANOI] Full-time High school/IELTS Teachers needed for our in-school teaching</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F16" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>High School, Salary 580000M VND, Subject match</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4399236048</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Legal &amp;amp; Teaching Jobs for Foreign Teachers in Vietnam</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>[CAN THO] PART - TIME ENGLISH TEACHERS AT ISMART EDUCATION</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>[CAN THO] PART - TIME ENGLISH TEACHERS AT ISMART EDUCATION</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>460,000 vnd</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Skip to main content
 LinkedIn
@@ -1289,89 +1353,39 @@
 Get AI-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F17" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>High School, Salary 460000M VND, Subject match</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4408677433</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Part-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>University of Economics Ho Chi Minh City (UEH)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>English Lecturer – Business English / IELTS</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Ho Chi Minh City</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>35,000,000 – 55,000,000 VND/month</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Master's in English, Linguistics or Education; university teaching experience; IELTS 8.0+ or equivalent</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Business English specialization (BA Business Management), IELTS teacher, university level</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Web Research</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ueh.edu.vn/tuyendung</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>VUS Smart English</t>
+          <t>University of Economics Ho Chi Minh City (UEH)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>English Teacher (IELTS / General English)</t>
+          <t>English Lecturer – Business English / IELTS</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1381,12 +1395,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12,000,000 – 18,000,000 VND/month</t>
+          <t>35,000,000 – 55,000,000 VND/month</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Bachelor's degree; TESOL/TEFL preferred; strong English skills; teaching experience valued</t>
+          <t>Master's in English, Linguistics or Education; university teaching experience; IELTS 8.0+ or equivalent</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
@@ -1394,7 +1408,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>IELTS, Grade 6+, HCMC; salary below 50M target but negotiable</t>
+          <t>Business English specialization (BA Business Management), IELTS teacher, university level</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1404,7 +1418,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://vus.edu.vn/tuyendung</t>
+          <t>https://www.ueh.edu.vn/tuyendung</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1416,25 +1430,75 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>VUS Smart English</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>English Teacher (IELTS / General English)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>12,000,000 – 18,000,000 VND/month</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Bachelor's degree; TESOL/TEFL preferred; strong English skills; teaching experience valued</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>IELTS, Grade 6+, HCMC; salary below 50M target but negotiable</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Web Research</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>https://vus.edu.vn/tuyendung</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Legal &amp;amp; Teaching Jobs for Foreign Teachers in Vietnam</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Full-time Public School Teachers in Ho Chi Minh | APPLY NOW!</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Locations: In Ho Chi Minh City at our ILA Go Vap centre.</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>600,000 VND</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Skip to main content
 LinkedIn
@@ -1453,52 +1517,52 @@
 Get AI</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F20" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Grade unspecified, Salary 600000M VND, Subject match, Full-time</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4386872829</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>TEFL UK</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Teach Vietnam - Major</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Ho Chi Minh City</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">350,000 VND </t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Skip to main content
 LinkedIn
@@ -1516,52 +1580,52 @@
 Stand out this spring with 35% off our 150-hour Advanced TEFL Course. Build the skills, confidence, and qualifications to land higher-paying roles anywhere in the world. Use code: SPRI</t>
         </is>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F21" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Grade unspecified, Salary 350000M VND, Subject match, Full-time</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4198828076</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Australian International School, Vietnam</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Secondary English Teacher (from Jan-2027)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Ho Chi Minh City, Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>730,000 VND</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Skip to main content
 LinkedIn
@@ -1581,52 +1645,52 @@
 Am</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F22" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Grade unspecified, Salary 730000M VND, Subject match, Full-time</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4413247154</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Atlantic Teacher Careers</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>[Ha Noi] Atlantic Five-Star English- Full-Time Secondary Teachers - 2026-2027</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Atlantic Teacher Careers  Hanoi Capital Region</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">730,000 VND </t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Skip to main content
 LinkedIn
@@ -1645,52 +1709,52 @@
 [Ha Noi] Atlantic Five-Star English- Full-Time S</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F23" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Grade unspecified, Salary 730000M VND, Subject match, Full-time</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4399222766</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Legal &amp; Teaching Jobs for Foreign Teachers in Vietnam</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Full-time Public School Teachers in Ho Chi Minh | APPLY NOW!</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Full-time Public School Teachers in Ho Chi Minh | APPLY NOW!</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>600,000 VND</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Skip to main content
 LinkedIn
@@ -1708,52 +1772,52 @@
 This Summer, ILA is hiring for posit</t>
         </is>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F24" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Grade unspecified, Salary 600000MM VND (target), Subject match, Full-time</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4386872829</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Legal &amp; Teaching Jobs for Foreign Teachers in Vietnam</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>[An Giang] FULLTIME ENGLISH TEACHERS</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>36,000,000 VND</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Skip to main content
 LinkedIn
@@ -1772,32 +1836,32 @@
 Negotiable salary: Up to 36,000,000 VND for 100 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F25" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Grade unspecified, Salary 36000000MM VND (target), Subject match, Full-time</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4414144018</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J24"/>
+  <autoFilter ref="A1:J25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>